--- a/GA_testcases/GAAN-933_REFERENCE_FORMAT_Component_Feature_Implementation.xlsx
+++ b/GA_testcases/GAAN-933_REFERENCE_FORMAT_Component_Feature_Implementation.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="685" uniqueCount="464">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="685" uniqueCount="460">
   <si>
     <t>TC_ID</t>
   </si>
@@ -89,7 +89,7 @@
   </si>
   <si>
     <t xml:space="preserve">• Open Figma design reference
-• Compare colors (purple header #6B46C1)
+• Compare colors (purple header)
 • Check spacing and padding
 • Verify typography matches</t>
   </si>
@@ -139,7 +139,7 @@
     <t>TC_006</t>
   </si>
   <si>
-    <t>Verify form submission</t>
+    <t>Verify form submission and data persistence</t>
   </si>
   <si>
     <t xml:space="preserve">• Fill all required form fields
@@ -151,13 +151,13 @@
     <t>Valid form data</t>
   </si>
   <si>
-    <t>Form submits successfully; Data persisted</t>
+    <t>Form submits successfully</t>
   </si>
   <si>
     <t>TC_007</t>
   </si>
   <si>
-    <t>Verify responsive behavior on target viewport</t>
+    <t>Verify responsive behavior</t>
   </si>
   <si>
     <t xml:space="preserve">• Test on multiple viewports
@@ -427,10 +427,685 @@
     <t>Concurrent user sessions</t>
   </si>
   <si>
-    <t>Concurrent edits handled; No data corruption</t>
+    <t>Concurrent edits handled</t>
   </si>
   <si>
     <t>TC_022</t>
+  </si>
+  <si>
+    <t>Accessibility</t>
+  </si>
+  <si>
+    <t>Verify WCAG 2.2 semantic HTML structure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Inspect HTML elements
+• Verify heading hierarchy (h1-h6)
+• Check list markup
+• Verify semantic tags used</t>
+  </si>
+  <si>
+    <t>HTML inspection tools (DevTools)</t>
+  </si>
+  <si>
+    <t>Semantic HTML structure correct</t>
+  </si>
+  <si>
+    <t>TC_023</t>
+  </si>
+  <si>
+    <t>Verify color contrast compliance (4.5:1 WCAG AA)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Use color contrast checker
+• Test purple header vs text
+• Test all text colors
+• Verify &gt;= 4.5:1 ratio</t>
+  </si>
+  <si>
+    <t>Contrast checking tool, Color palette</t>
+  </si>
+  <si>
+    <t>All contrasts &gt;= 4.5:1</t>
+  </si>
+  <si>
+    <t>TC_024</t>
+  </si>
+  <si>
+    <t>Verify screen reader compatibility</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Test with NVDA/JAWS
+• Verify text alternatives
+• Check aria-labels
+• Verify reading order</t>
+  </si>
+  <si>
+    <t>Screen reader software (NVDA)</t>
+  </si>
+  <si>
+    <t>Content readable via screen reader</t>
+  </si>
+  <si>
+    <t>TC_025</t>
+  </si>
+  <si>
+    <t>Verify keyboard navigation (Tab order)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Navigate using Tab key only
+• Verify logical tab order
+• Check focus indicators
+• Test all interactive elements</t>
+  </si>
+  <si>
+    <t>Keyboard (Tab/Shift+Tab)</t>
+  </si>
+  <si>
+    <t>Fully keyboard navigable</t>
+  </si>
+  <si>
+    <t>TC_026</t>
+  </si>
+  <si>
+    <t>Verify 200% zoom readability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Zoom page to 200%
+• Verify no content cut off
+• Check text remains readable
+• Verify layout flows</t>
+  </si>
+  <si>
+    <t>Browser zoom at 200%</t>
+  </si>
+  <si>
+    <t>Content readable at 200% zoom</t>
+  </si>
+  <si>
+    <t>TC_027</t>
+  </si>
+  <si>
+    <t>Verify no critical accessibility violations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Run Level Access scan
+• Check for WCAG violations
+• Verify no errors
+• Document any warnings</t>
+  </si>
+  <si>
+    <t>Level Access scan tool</t>
+  </si>
+  <si>
+    <t>No critical issues found</t>
+  </si>
+  <si>
+    <t>TC_028</t>
+  </si>
+  <si>
+    <t>Verify mobile touch target sizes (44x44px)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Test on actual mobile device
+• Check all clickable areas
+• Verify each &gt;= 44x44px
+• Check spacing between targets</t>
+  </si>
+  <si>
+    <t>WCAG 2.5.5: 44x44px minimum</t>
+  </si>
+  <si>
+    <t>Touch targets meet WCAG minimum</t>
+  </si>
+  <si>
+    <t>TC_029</t>
+  </si>
+  <si>
+    <t>Responsive</t>
+  </si>
+  <si>
+    <t>Verify mobile small (320px)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Set viewport 320x568
+• Verify single-column layout
+• Verify full-width
+• Check readable text</t>
+  </si>
+  <si>
+    <t>320x568px (Mobile small)</t>
+  </si>
+  <si>
+    <t>Displays correctly on 320px</t>
+  </si>
+  <si>
+    <t>TC_030</t>
+  </si>
+  <si>
+    <t>Verify mobile large (414px)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Set viewport 414x896
+• Verify single column layout
+• Verify spacing adequate
+• Check readable</t>
+  </si>
+  <si>
+    <t>414x896px (Mobile large)</t>
+  </si>
+  <si>
+    <t>Displays correctly on 414px</t>
+  </si>
+  <si>
+    <t>TC_031</t>
+  </si>
+  <si>
+    <t>Verify tablet portrait (768px)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Set viewport 768x1024
+• Verify optimized layout
+• Check element spacing
+• Verify readable</t>
+  </si>
+  <si>
+    <t>768x1024px (Tablet Portrait)</t>
+  </si>
+  <si>
+    <t>Tablet layout correct</t>
+  </si>
+  <si>
+    <t>TC_032</t>
+  </si>
+  <si>
+    <t>Verify tablet landscape (1024px)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Set viewport 1024x768
+• Verify horizontal layout
+• Check spacing correct
+• Verify readable</t>
+  </si>
+  <si>
+    <t>1024x768px (Tablet Landscape)</t>
+  </si>
+  <si>
+    <t>Tablet landscape displays correctly</t>
+  </si>
+  <si>
+    <t>TC_033</t>
+  </si>
+  <si>
+    <t>Verify desktop standard (1366px)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Set viewport 1366x768
+• Verify layout optimized
+• Verify spacing
+• Check readable</t>
+  </si>
+  <si>
+    <t>1366x768px (Desktop)</t>
+  </si>
+  <si>
+    <t>Desktop standard displays correctly</t>
+  </si>
+  <si>
+    <t>TC_034</t>
+  </si>
+  <si>
+    <t>Verify desktop large (1920px)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Set viewport 1920x1080
+• Verify two-column layout
+• Check statistics LEFT, bullets RIGHT
+• Verify optimal spacing</t>
+  </si>
+  <si>
+    <t>1920x1080px (Desktop large)</t>
+  </si>
+  <si>
+    <t>Large desktop displays correctly</t>
+  </si>
+  <si>
+    <t>TC_035</t>
+  </si>
+  <si>
+    <t>Verify ultra wide (2560px) - 4K</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Set viewport 2560x1440
+• Verify layout correct
+• Verify not too stretched
+• Verify readable</t>
+  </si>
+  <si>
+    <t>2560x1440px (Ultra wide 4K)</t>
+  </si>
+  <si>
+    <t>Ultra wide displays correctly</t>
+  </si>
+  <si>
+    <t>TC_036</t>
+  </si>
+  <si>
+    <t>Verify layout transition points</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Test 768px to 1024px transition
+• Test 1024px to 1920px transition
+• Verify smooth breakpoints
+• Check no layout jump</t>
+  </si>
+  <si>
+    <t>Incremental viewport changes</t>
+  </si>
+  <si>
+    <t>Smooth transitions at breakpoints</t>
+  </si>
+  <si>
+    <t>TC_037</t>
+  </si>
+  <si>
+    <t>Verify full-width content display</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Verify component uses full width
+• Check padding consistency
+• Verify margins appropriate
+• Check not stretched</t>
+  </si>
+  <si>
+    <t>Various screen sizes</t>
+  </si>
+  <si>
+    <t>Full-width display correct</t>
+  </si>
+  <si>
+    <t>TC_038</t>
+  </si>
+  <si>
+    <t>Cross-Browser</t>
+  </si>
+  <si>
+    <t>Verify Chrome desktop rendering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Open in Chrome latest
+• Verify all elements display
+• Check styling correct
+• Verify no console errors</t>
+  </si>
+  <si>
+    <t>Chrome browser (desktop)</t>
+  </si>
+  <si>
+    <t>Renders correctly in Chrome</t>
+  </si>
+  <si>
+    <t>TC_039</t>
+  </si>
+  <si>
+    <t>Verify Firefox desktop rendering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Open in Firefox latest
+• Verify styling consistent
+• Check layout correct
+• Verify functionality</t>
+  </si>
+  <si>
+    <t>Firefox browser (desktop)</t>
+  </si>
+  <si>
+    <t>Renders correctly in Firefox</t>
+  </si>
+  <si>
+    <t>TC_040</t>
+  </si>
+  <si>
+    <t>Verify Safari desktop rendering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Open in Safari latest
+• Check -webkit prefixes
+• Verify styling correct
+• Check all features work</t>
+  </si>
+  <si>
+    <t>Safari browser (desktop)</t>
+  </si>
+  <si>
+    <t>Renders correctly in Safari</t>
+  </si>
+  <si>
+    <t>TC_041</t>
+  </si>
+  <si>
+    <t>Verify Edge desktop rendering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Open in Edge latest
+• Verify compatibility
+• Check styling
+• Test functionality</t>
+  </si>
+  <si>
+    <t>Microsoft Edge browser</t>
+  </si>
+  <si>
+    <t>Renders correctly in Edge</t>
+  </si>
+  <si>
+    <t>TC_042</t>
+  </si>
+  <si>
+    <t>Verify Safari mobile rendering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Test on iPhone Safari
+• Verify responsive layout
+• Check touch interactions
+• Verify performance</t>
+  </si>
+  <si>
+    <t>iPhone Safari mobile</t>
+  </si>
+  <si>
+    <t>Works correctly on Safari mobile</t>
+  </si>
+  <si>
+    <t>TC_043</t>
+  </si>
+  <si>
+    <t>Verify Chrome mobile rendering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Test on Chrome mobile
+• Verify responsive behavior
+• Check touch targets
+• Verify no zoom needed</t>
+  </si>
+  <si>
+    <t>Chrome mobile browser</t>
+  </si>
+  <si>
+    <t>Works correctly on Chrome mobile</t>
+  </si>
+  <si>
+    <t>TC_044</t>
+  </si>
+  <si>
+    <t>Verify consistent behavior across browsers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Compare rendering across browsers
+• Check for browser-specific issues
+• Verify consistent user experience
+• Document differences</t>
+  </si>
+  <si>
+    <t>Multiple browser versions</t>
+  </si>
+  <si>
+    <t>Behavior consistent across browsers</t>
+  </si>
+  <si>
+    <t>TC_045</t>
+  </si>
+  <si>
+    <t>UI</t>
+  </si>
+  <si>
+    <t>Verify purple header bar styling</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Check header background color
+• Verify hex #6B46C1 or equivalent
+• Check padding/spacing
+• Verify text color white</t>
+  </si>
+  <si>
+    <t>Purple header (#6B46C1)</t>
+  </si>
+  <si>
+    <t>Header styled correctly</t>
+  </si>
+  <si>
+    <t>TC_046</t>
+  </si>
+  <si>
+    <t>Verify typography and font sizes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Check title font size
+• Verify body text size
+• Check line spacing
+• Verify font family consistent</t>
+  </si>
+  <si>
+    <t>Figma design specs</t>
+  </si>
+  <si>
+    <t>Typography matches spec</t>
+  </si>
+  <si>
+    <t>TC_047</t>
+  </si>
+  <si>
+    <t>Verify spacing and padding consistency</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Measure margins between elements
+• Check padding inside containers
+• Verify whitespace balance
+• Compare with Figma</t>
+  </si>
+  <si>
+    <t>Spacing measurements</t>
+  </si>
+  <si>
+    <t>Spacing matches design</t>
+  </si>
+  <si>
+    <t>TC_048</t>
+  </si>
+  <si>
+    <t>Verify bullet point formatting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Check bullet symbol
+• Verify indentation
+• Check line height
+• Verify alignment</t>
+  </si>
+  <si>
+    <t>Bullet list component</t>
+  </si>
+  <si>
+    <t>Bullet formatting correct</t>
+  </si>
+  <si>
+    <t>TC_049</t>
+  </si>
+  <si>
+    <t>Verify statistical block display</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Check number display
+• Verify label text
+• Check icon display
+• Verify alignment in layout</t>
+  </si>
+  <si>
+    <t>Statistics block data</t>
+  </si>
+  <si>
+    <t>Statistics display correctly</t>
+  </si>
+  <si>
+    <t>TC_050</t>
+  </si>
+  <si>
+    <t>Verify borders and dividers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Check for dividers between sections
+• Verify border colors
+• Check border width
+• Verify alignment</t>
+  </si>
+  <si>
+    <t>Component layout</t>
+  </si>
+  <si>
+    <t>Borders display correctly</t>
+  </si>
+  <si>
+    <t>TC_051</t>
+  </si>
+  <si>
+    <t>Verify visual hierarchy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Check title prominence
+• Verify emphasis on key elements
+• Check visual weight
+• Verify focus areas clear</t>
+  </si>
+  <si>
+    <t>Visual design review</t>
+  </si>
+  <si>
+    <t>Hierarchy is clear</t>
+  </si>
+  <si>
+    <t>TC_052</t>
+  </si>
+  <si>
+    <t>Performance</t>
+  </si>
+  <si>
+    <t>Verify page load time performance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Load component page
+• Measure load time
+• Check network requests
+• Verify &lt; 3 second load</t>
+  </si>
+  <si>
+    <t>Network throttling (3G, 4G)</t>
+  </si>
+  <si>
+    <t>Page loads &lt; 3 seconds</t>
+  </si>
+  <si>
+    <t>TC_053</t>
+  </si>
+  <si>
+    <t>Verify large dataset performance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Load 1000+ records
+• Check rendering performance
+• Verify no lag
+• Check memory usage</t>
+  </si>
+  <si>
+    <t>Large dataset (1000+ items)</t>
+  </si>
+  <si>
+    <t>Handles large data efficiently</t>
+  </si>
+  <si>
+    <t>TC_054</t>
+  </si>
+  <si>
+    <t>Verify image optimization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Check image sizes
+• Verify responsive images
+• Check lazy loading
+• Verify format optimization</t>
+  </si>
+  <si>
+    <t>Image files and assets</t>
+  </si>
+  <si>
+    <t>Images optimized and responsive</t>
+  </si>
+  <si>
+    <t>TC_055</t>
+  </si>
+  <si>
+    <t>Integration</t>
+  </si>
+  <si>
+    <t>Verify API integration</t>
+  </si>
+  <si>
+    <t>API endpoint available</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Call API endpoint
+• Verify response format
+• Check data transformation
+• Verify UI updates</t>
+  </si>
+  <si>
+    <t>API endpoint, request data</t>
+  </si>
+  <si>
+    <t>API integration works correctly</t>
+  </si>
+  <si>
+    <t>TC_056</t>
+  </si>
+  <si>
+    <t>Verify database persistence</t>
+  </si>
+  <si>
+    <t>Database connection active</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Submit form data
+• Verify database entry
+• Retrieve data
+• Verify data integrity</t>
+  </si>
+  <si>
+    <t>Form data, database connection</t>
+  </si>
+  <si>
+    <t>Data persisted correctly in database</t>
+  </si>
+  <si>
+    <t>TC_057</t>
+  </si>
+  <si>
+    <t>Verify third-party service integration</t>
+  </si>
+  <si>
+    <t>Third-party services configured</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Call third-party API
+• Verify integration working
+• Check error handling
+• Verify data sync</t>
+  </si>
+  <si>
+    <t>Third-party service credentials</t>
+  </si>
+  <si>
+    <t>Third-party services integrated correctly</t>
+  </si>
+  <si>
+    <t>TC_058</t>
   </si>
   <si>
     <t>Security</t>
@@ -448,10 +1123,10 @@
     <t>'; DROP TABLE--; SELECT * FROM;</t>
   </si>
   <si>
-    <t>SQL injection prevented; Input validated</t>
-  </si>
-  <si>
-    <t>TC_023</t>
+    <t>SQL injection prevented</t>
+  </si>
+  <si>
+    <t>TC_059</t>
   </si>
   <si>
     <t>Verify CSRF attack prevention</t>
@@ -466,10 +1141,10 @@
     <t>CSRF token verification</t>
   </si>
   <si>
-    <t>CSRF tokens validated; Attacks prevented</t>
-  </si>
-  <si>
-    <t>TC_024</t>
+    <t>CSRF tokens validated</t>
+  </si>
+  <si>
+    <t>TC_060</t>
   </si>
   <si>
     <t>Verify secure authentication</t>
@@ -487,10 +1162,10 @@
     <t>User credentials</t>
   </si>
   <si>
-    <t>Credentials secure; HTTPS enforced</t>
-  </si>
-  <si>
-    <t>TC_025</t>
+    <t>Credentials secure</t>
+  </si>
+  <si>
+    <t>TC_061</t>
   </si>
   <si>
     <t>Verify data encryption</t>
@@ -511,700 +1186,25 @@
     <t>Data encrypted at rest and in transit</t>
   </si>
   <si>
-    <t>TC_026</t>
-  </si>
-  <si>
-    <t>Accessibility</t>
-  </si>
-  <si>
-    <t>Verify WCAG 2.2 semantic HTML structure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• Inspect HTML elements
-• Verify heading hierarchy (h1-h6)
-• Check list markup
-• Verify semantic tags used</t>
-  </si>
-  <si>
-    <t>HTML inspection tools (DevTools)</t>
-  </si>
-  <si>
-    <t>Semantic HTML structure correct</t>
-  </si>
-  <si>
-    <t>TC_027</t>
-  </si>
-  <si>
-    <t>Verify color contrast compliance (4.5:1 WCAG AA)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• Use color contrast checker
-• Test purple header vs text
-• Test all text colors
-• Verify &gt;= 4.5:1 ratio</t>
-  </si>
-  <si>
-    <t>Contrast checking tool, Color palette</t>
-  </si>
-  <si>
-    <t>All contrasts &gt;= 4.5:1</t>
-  </si>
-  <si>
-    <t>TC_028</t>
-  </si>
-  <si>
-    <t>Verify screen reader compatibility</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• Test with NVDA/JAWS
-• Verify text alternatives
-• Check aria-labels
-• Verify reading order</t>
-  </si>
-  <si>
-    <t>Screen reader software (NVDA)</t>
-  </si>
-  <si>
-    <t>Content readable via screen reader</t>
-  </si>
-  <si>
-    <t>TC_029</t>
-  </si>
-  <si>
-    <t>Verify keyboard navigation (Tab order)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• Navigate using Tab key only
-• Verify logical tab order
-• Check focus indicators
-• Test all interactive elements</t>
-  </si>
-  <si>
-    <t>Keyboard (Tab/Shift+Tab)</t>
-  </si>
-  <si>
-    <t>Fully keyboard navigable</t>
-  </si>
-  <si>
-    <t>TC_030</t>
-  </si>
-  <si>
-    <t>Verify 200% zoom readability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• Zoom page to 200%
-• Verify no content cut off
-• Check text remains readable
-• Verify layout flows</t>
-  </si>
-  <si>
-    <t>Browser zoom at 200%</t>
-  </si>
-  <si>
-    <t>Content readable at 200% zoom</t>
-  </si>
-  <si>
-    <t>TC_031</t>
-  </si>
-  <si>
-    <t>Verify no critical accessibility violations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• Run Level Access scan
-• Check for WCAG violations
-• Verify no errors
-• Document any warnings</t>
-  </si>
-  <si>
-    <t>Level Access scan tool</t>
-  </si>
-  <si>
-    <t>No critical issues found</t>
-  </si>
-  <si>
-    <t>TC_032</t>
-  </si>
-  <si>
-    <t>Verify mobile touch target sizes (44x44px)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• Test on actual mobile device
-• Check all clickable areas
-• Verify each &gt;= 44x44px
-• Check spacing between targets</t>
-  </si>
-  <si>
-    <t>WCAG 2.5.5: 44x44px minimum</t>
-  </si>
-  <si>
-    <t>Touch targets meet WCAG minimum</t>
-  </si>
-  <si>
-    <t>TC_033</t>
-  </si>
-  <si>
-    <t>Responsive</t>
-  </si>
-  <si>
-    <t>Verify mobile small (320px)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• Set viewport 320x568
-• Verify single-column layout
-• Verify full-width
-• Check readable text</t>
-  </si>
-  <si>
-    <t>320x568px (Mobile small)</t>
-  </si>
-  <si>
-    <t>Displays correctly on 320px</t>
-  </si>
-  <si>
-    <t>TC_034</t>
-  </si>
-  <si>
-    <t>Verify mobile large (414px)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• Set viewport 414x896
-• Verify single column layout
-• Verify spacing adequate
-• Check readable</t>
-  </si>
-  <si>
-    <t>414x896px (Mobile large)</t>
-  </si>
-  <si>
-    <t>Displays correctly on 414px</t>
-  </si>
-  <si>
-    <t>TC_035</t>
-  </si>
-  <si>
-    <t>Verify tablet portrait (768px)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• Set viewport 768x1024
-• Verify optimized layout
-• Check element spacing
-• Verify readable</t>
-  </si>
-  <si>
-    <t>768x1024px (Tablet Portrait)</t>
-  </si>
-  <si>
-    <t>Tablet layout correct</t>
-  </si>
-  <si>
-    <t>TC_036</t>
-  </si>
-  <si>
-    <t>Verify tablet landscape (1024px)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• Set viewport 1024x768
-• Verify horizontal layout
-• Check spacing correct
-• Verify readable</t>
-  </si>
-  <si>
-    <t>1024x768px (Tablet Landscape)</t>
-  </si>
-  <si>
-    <t>Tablet landscape displays correctly</t>
-  </si>
-  <si>
-    <t>TC_037</t>
-  </si>
-  <si>
-    <t>Verify desktop standard (1366px)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• Set viewport 1366x768
-• Verify layout optimized
-• Verify spacing
-• Check readable</t>
-  </si>
-  <si>
-    <t>1366x768px (Desktop)</t>
-  </si>
-  <si>
-    <t>Desktop standard displays correctly</t>
-  </si>
-  <si>
-    <t>TC_038</t>
-  </si>
-  <si>
-    <t>Verify desktop large (1920px)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• Set viewport 1920x1080
-• Verify two-column layout
-• Check statistics LEFT, bullets RIGHT
-• Verify optimal spacing</t>
-  </si>
-  <si>
-    <t>1920x1080px (Desktop large)</t>
-  </si>
-  <si>
-    <t>Large desktop displays correctly</t>
-  </si>
-  <si>
-    <t>TC_039</t>
-  </si>
-  <si>
-    <t>Verify ultra wide (2560px) - 4K</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• Set viewport 2560x1440
-• Verify layout correct
-• Verify not too stretched
-• Verify readable</t>
-  </si>
-  <si>
-    <t>2560x1440px (Ultra wide 4K)</t>
-  </si>
-  <si>
-    <t>Ultra wide displays correctly</t>
-  </si>
-  <si>
-    <t>TC_040</t>
-  </si>
-  <si>
-    <t>Verify layout transition points</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• Test 768px to 1024px transition
-• Test 1024px to 1920px transition
-• Verify smooth breakpoints
-• Check no layout jump</t>
-  </si>
-  <si>
-    <t>Incremental viewport changes</t>
-  </si>
-  <si>
-    <t>Smooth transitions at breakpoints</t>
-  </si>
-  <si>
-    <t>TC_041</t>
-  </si>
-  <si>
-    <t>Verify full-width content display</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• Verify component uses full width
-• Check padding consistency
-• Verify margins appropriate
-• Check not stretched</t>
-  </si>
-  <si>
-    <t>Various screen sizes</t>
-  </si>
-  <si>
-    <t>Full-width display correct</t>
-  </si>
-  <si>
-    <t>TC_042</t>
-  </si>
-  <si>
-    <t>UI</t>
-  </si>
-  <si>
-    <t>Verify purple header bar styling</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• Check header background color
-• Verify hex #6B46C1 or equivalent
-• Check padding/spacing
-• Verify text color white</t>
-  </si>
-  <si>
-    <t>Purple header (#6B46C1)</t>
-  </si>
-  <si>
-    <t>Header styled correctly</t>
-  </si>
-  <si>
-    <t>TC_043</t>
-  </si>
-  <si>
-    <t>Verify typography and font sizes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• Check title font size
-• Verify body text size
-• Check line spacing
-• Verify font family consistent</t>
-  </si>
-  <si>
-    <t>Figma design specs</t>
-  </si>
-  <si>
-    <t>Typography matches spec</t>
-  </si>
-  <si>
-    <t>TC_044</t>
-  </si>
-  <si>
-    <t>Verify spacing and padding consistency</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• Measure margins between elements
-• Check padding inside containers
-• Verify whitespace balance
-• Compare with Figma</t>
-  </si>
-  <si>
-    <t>Spacing measurements</t>
-  </si>
-  <si>
-    <t>Spacing matches design</t>
-  </si>
-  <si>
-    <t>TC_045</t>
-  </si>
-  <si>
-    <t>Verify bullet point formatting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• Check bullet symbol
-• Verify indentation
-• Check line height
-• Verify alignment</t>
-  </si>
-  <si>
-    <t>Bullet list component</t>
-  </si>
-  <si>
-    <t>Bullet formatting correct</t>
-  </si>
-  <si>
-    <t>TC_046</t>
-  </si>
-  <si>
-    <t>Verify statistical block display</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• Check number display
-• Verify label text
-• Check icon display
-• Verify alignment in layout</t>
-  </si>
-  <si>
-    <t>Statistics block data</t>
-  </si>
-  <si>
-    <t>Statistics display correctly</t>
-  </si>
-  <si>
-    <t>TC_047</t>
-  </si>
-  <si>
-    <t>Verify visual hierarchy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• Check title prominence
-• Verify emphasis on key elements
-• Check visual weight
-• Verify focus areas clear</t>
-  </si>
-  <si>
-    <t>Visual design review</t>
-  </si>
-  <si>
-    <t>Hierarchy is clear</t>
-  </si>
-  <si>
-    <t>TC_048</t>
-  </si>
-  <si>
-    <t>Verify hover and focus states</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• Check button hover color
-• Verify focus outline visible
-• Check transition smooth
-• Verify all interactive elements have states</t>
-  </si>
-  <si>
-    <t>Interactive element states</t>
-  </si>
-  <si>
-    <t>States display correctly</t>
-  </si>
-  <si>
-    <t>TC_049</t>
-  </si>
-  <si>
-    <t>Cross-Browser</t>
-  </si>
-  <si>
-    <t>Verify Chrome desktop rendering</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• Open in Chrome latest
-• Verify all elements display
-• Check styling correct
-• Verify no console errors</t>
-  </si>
-  <si>
-    <t>Chrome browser (desktop)</t>
-  </si>
-  <si>
-    <t>Renders correctly in Chrome</t>
-  </si>
-  <si>
-    <t>TC_050</t>
-  </si>
-  <si>
-    <t>Verify Firefox desktop rendering</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• Open in Firefox latest
-• Verify styling consistent
-• Check layout correct
-• Verify functionality</t>
-  </si>
-  <si>
-    <t>Firefox browser (desktop)</t>
-  </si>
-  <si>
-    <t>Renders correctly in Firefox</t>
-  </si>
-  <si>
-    <t>TC_051</t>
-  </si>
-  <si>
-    <t>Verify Safari desktop rendering</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• Open in Safari latest
-• Check -webkit prefixes
-• Verify styling correct
-• Check all features work</t>
-  </si>
-  <si>
-    <t>Safari browser (desktop)</t>
-  </si>
-  <si>
-    <t>Renders correctly in Safari</t>
-  </si>
-  <si>
-    <t>TC_052</t>
-  </si>
-  <si>
-    <t>Verify Edge desktop rendering</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• Open in Edge latest
-• Verify compatibility
-• Check styling
-• Test functionality</t>
-  </si>
-  <si>
-    <t>Microsoft Edge browser</t>
-  </si>
-  <si>
-    <t>Renders correctly in Edge</t>
-  </si>
-  <si>
-    <t>TC_053</t>
-  </si>
-  <si>
-    <t>Verify Safari mobile rendering</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• Test on iPhone Safari
-• Verify responsive layout
-• Check touch interactions
-• Verify performance</t>
-  </si>
-  <si>
-    <t>iPhone Safari mobile</t>
-  </si>
-  <si>
-    <t>Works correctly on Safari mobile</t>
-  </si>
-  <si>
-    <t>TC_054</t>
-  </si>
-  <si>
-    <t>Verify Chrome mobile rendering</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• Test on Chrome mobile
-• Verify responsive behavior
-• Check touch targets
-• Verify no zoom needed</t>
-  </si>
-  <si>
-    <t>Chrome mobile browser</t>
-  </si>
-  <si>
-    <t>Works correctly on Chrome mobile</t>
-  </si>
-  <si>
-    <t>TC_055</t>
-  </si>
-  <si>
-    <t>Verify API response handling</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• Test with valid API response
-• Test null response
-• Test malformed data
-• Verify error handling</t>
-  </si>
-  <si>
-    <t>API endpoints and responses</t>
-  </si>
-  <si>
-    <t>Responses handled correctly</t>
-  </si>
-  <si>
-    <t>TC_056</t>
-  </si>
-  <si>
-    <t>Performance</t>
-  </si>
-  <si>
-    <t>Verify page load time performance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• Load component page
-• Measure load time
-• Check network requests
-• Verify &lt; 3 second load</t>
-  </si>
-  <si>
-    <t>Network throttling (3G, 4G)</t>
-  </si>
-  <si>
-    <t>Page loads &lt; 3 seconds</t>
-  </si>
-  <si>
-    <t>TC_057</t>
-  </si>
-  <si>
-    <t>Verify large dataset performance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• Load 1000+ records
-• Check rendering performance
-• Verify no lag
-• Check memory usage</t>
-  </si>
-  <si>
-    <t>Large dataset (1000+ items)</t>
-  </si>
-  <si>
-    <t>Handles large data efficiently</t>
-  </si>
-  <si>
-    <t>TC_058</t>
-  </si>
-  <si>
-    <t>Verify image optimization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• Check image sizes
-• Verify responsive images
-• Check lazy loading
-• Verify format optimization</t>
-  </si>
-  <si>
-    <t>Image files and assets</t>
-  </si>
-  <si>
-    <t>Images optimized and responsive</t>
-  </si>
-  <si>
-    <t>TC_059</t>
-  </si>
-  <si>
-    <t>Integration</t>
-  </si>
-  <si>
-    <t>Verify API integration</t>
-  </si>
-  <si>
-    <t>API endpoint available</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• Call API endpoint
-• Verify response format
-• Check data transformation
-• Verify UI updates</t>
-  </si>
-  <si>
-    <t>API endpoint, request data</t>
-  </si>
-  <si>
-    <t>API integration works correctly</t>
-  </si>
-  <si>
-    <t>TC_060</t>
-  </si>
-  <si>
-    <t>Verify database persistence</t>
-  </si>
-  <si>
-    <t>Database connection active</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• Submit form data
-• Verify database entry
-• Retrieve data
-• Verify data integrity</t>
-  </si>
-  <si>
-    <t>Form data, database connection</t>
-  </si>
-  <si>
-    <t>Data persisted correctly in database</t>
-  </si>
-  <si>
-    <t>TC_061</t>
-  </si>
-  <si>
-    <t>Verify third-party service integration</t>
-  </si>
-  <si>
-    <t>Third-party services configured</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• Call third-party API
-• Verify integration working
-• Check error handling
-• Verify data sync</t>
-  </si>
-  <si>
-    <t>Third-party service credentials</t>
-  </si>
-  <si>
-    <t>Third-party services integrated correctly</t>
-  </si>
-  <si>
     <t>TC_062</t>
   </si>
   <si>
     <t>Boundary Value</t>
   </si>
   <si>
-    <t>Verify minimum numeric value handling</t>
-  </si>
-  <si>
-    <t>Numeric input field exists</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• Enter minimum value (0 or 1)
+    <t>Verify minimum numeric value (0)</t>
+  </si>
+  <si>
+    <t>Numeric field exists</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Enter minimum value (0)
 • Verify input accepted
 • Check processing correct
 • Verify no errors</t>
   </si>
   <si>
-    <t>0, 1, -999999</t>
+    <t>0</t>
   </si>
   <si>
     <t>Minimum values handled correctly</t>
@@ -1213,7 +1213,7 @@
     <t>TC_063</t>
   </si>
   <si>
-    <t>Verify maximum numeric value handling</t>
+    <t>Verify maximum numeric value</t>
   </si>
   <si>
     <t xml:space="preserve">• Enter maximum value
@@ -1231,10 +1231,7 @@
     <t>TC_064</t>
   </si>
   <si>
-    <t>Verify zero value handling</t>
-  </si>
-  <si>
-    <t>Numeric field exists</t>
+    <t>Verify zero value in calculations</t>
   </si>
   <si>
     <t xml:space="preserve">• Enter zero
@@ -1243,9 +1240,6 @@
 • Verify no division errors</t>
   </si>
   <si>
-    <t>0</t>
-  </si>
-  <si>
     <t>Zero handled appropriately</t>
   </si>
   <si>
@@ -1270,7 +1264,7 @@
     <t>TC_066</t>
   </si>
   <si>
-    <t>Verify decimal number handling</t>
+    <t>Verify decimal precision</t>
   </si>
   <si>
     <t xml:space="preserve">• Enter decimal values
@@ -1288,7 +1282,7 @@
     <t>TC_067</t>
   </si>
   <si>
-    <t>Verify very large number handling</t>
+    <t>Verify very large numbers</t>
   </si>
   <si>
     <t xml:space="preserve">• Enter very large numbers
@@ -1306,7 +1300,7 @@
     <t>TC_068</t>
   </si>
   <si>
-    <t>Verify number with leading zeros</t>
+    <t>Verify leading zeros in numbers</t>
   </si>
   <si>
     <t xml:space="preserve">• Enter numbers with leading zeros
@@ -1324,7 +1318,7 @@
     <t>TC_069</t>
   </si>
   <si>
-    <t>Verify scientific notation handling</t>
+    <t>Verify scientific notation</t>
   </si>
   <si>
     <t xml:space="preserve">• Enter scientific notation
@@ -1345,7 +1339,7 @@
     <t>Verify empty string handling</t>
   </si>
   <si>
-    <t>String input field exists</t>
+    <t>String field exists</t>
   </si>
   <si>
     <t xml:space="preserve">• Submit empty string
@@ -1366,9 +1360,6 @@
     <t>Verify single character string</t>
   </si>
   <si>
-    <t>String field exists</t>
-  </si>
-  <si>
     <t xml:space="preserve">• Enter single character
 • Verify accepted
 • Check storage
@@ -1405,7 +1396,7 @@
     <t>TC_073</t>
   </si>
   <si>
-    <t>Verify string with whitespace only</t>
+    <t>Verify whitespace-only string</t>
   </si>
   <si>
     <t xml:space="preserve">• Enter spaces only
@@ -1424,7 +1415,7 @@
     <t>TC_074</t>
   </si>
   <si>
-    <t>Verify string encoding (UTF-8, Unicode)</t>
+    <t>Verify Unicode and special characters</t>
   </si>
   <si>
     <t xml:space="preserve">• Enter Unicode characters
@@ -1481,7 +1472,7 @@
     <t>TC_077</t>
   </si>
   <si>
-    <t>Verify leap year date handling</t>
+    <t>Verify leap year handling</t>
   </si>
   <si>
     <t xml:space="preserve">• Enter leap year date (Feb 29)
@@ -1499,7 +1490,7 @@
     <t>TC_078</t>
   </si>
   <si>
-    <t>Verify invalid date format handling</t>
+    <t>Verify invalid date format</t>
   </si>
   <si>
     <t xml:space="preserve">• Enter invalid dates
@@ -1508,7 +1499,7 @@
 • Check validation</t>
   </si>
   <si>
-    <t>32-13-2024, 13/32/2024, invalid</t>
+    <t>32-13-2024, 13/32/2024</t>
   </si>
   <si>
     <t>Invalid dates rejected with validation</t>
@@ -1520,7 +1511,7 @@
     <t>Verify empty array handling</t>
   </si>
   <si>
-    <t>Array field or list exists</t>
+    <t>Array field exists</t>
   </si>
   <si>
     <t xml:space="preserve">• Submit empty array
@@ -1541,9 +1532,6 @@
     <t>Verify single item array</t>
   </si>
   <si>
-    <t>Array field exists</t>
-  </si>
-  <si>
     <t xml:space="preserve">• Submit array with one item
 • Verify accepted
 • Check processing
@@ -1571,7 +1559,7 @@
     <t>1000+ items, 10000+ items</t>
   </si>
   <si>
-    <t>Array size limits enforced; Performance acceptable</t>
+    <t>Array size limits enforced</t>
   </si>
   <si>
     <t>TC_082</t>
@@ -1613,7 +1601,7 @@
     <t>undefined, missing field</t>
   </si>
   <si>
-    <t>Undefined values handled with defaults or errors</t>
+    <t>Undefined values handled with defaults</t>
   </si>
   <si>
     <t>TEST CASE SUMMARY</t>
@@ -1631,19 +1619,19 @@
     <t>Edge Case Test Cases</t>
   </si>
   <si>
+    <t>Accessibility Test Cases</t>
+  </si>
+  <si>
+    <t>Responsive Test Cases</t>
+  </si>
+  <si>
+    <t>Cross-Browser Test Cases</t>
+  </si>
+  <si>
+    <t>UI Test Cases</t>
+  </si>
+  <si>
     <t>Security Test Cases</t>
-  </si>
-  <si>
-    <t>Accessibility Test Cases</t>
-  </si>
-  <si>
-    <t>Responsive Test Cases</t>
-  </si>
-  <si>
-    <t>UI Test Cases</t>
-  </si>
-  <si>
-    <t>Cross-Browser Test Cases</t>
   </si>
   <si>
     <t>Performance Test Cases</t>
@@ -2711,16 +2699,16 @@
         <v>130</v>
       </c>
       <c r="D25" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E25" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="E25" s="3" t="s">
+      <c r="F25" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="F25" s="3" t="s">
+      <c r="G25" s="3" t="s">
         <v>133</v>
-      </c>
-      <c r="G25" s="3" t="s">
-        <v>134</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>15</v>
@@ -2728,25 +2716,25 @@
     </row>
     <row r="26" ht="60" customHeight="1" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>119</v>
       </c>
       <c r="C26" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E26" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="D26" s="2" t="s">
+      <c r="F26" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="E26" s="2" t="s">
+      <c r="G26" s="2" t="s">
         <v>138</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>140</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>15</v>
@@ -2754,25 +2742,25 @@
     </row>
     <row r="27" ht="60" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E27" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="F27" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="C27" s="3" t="s">
+      <c r="G27" s="3" t="s">
         <v>143</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E27" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="G27" s="3" t="s">
-        <v>146</v>
       </c>
       <c r="H27" s="3" t="s">
         <v>15</v>
@@ -2780,25 +2768,25 @@
     </row>
     <row r="28" ht="60" customHeight="1" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="F28" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="B28" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="C28" s="2" t="s">
+      <c r="G28" s="2" t="s">
         <v>148</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>151</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>15</v>
@@ -2806,25 +2794,25 @@
     </row>
     <row r="29" ht="60" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="F29" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="B29" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="C29" s="3" t="s">
+      <c r="G29" s="3" t="s">
         <v>153</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>156</v>
       </c>
       <c r="H29" s="3" t="s">
         <v>15</v>
@@ -2832,25 +2820,25 @@
     </row>
     <row r="30" ht="60" customHeight="1" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E30" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="B30" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="C30" s="2" t="s">
+      <c r="F30" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="D30" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E30" s="2" t="s">
+      <c r="G30" s="2" t="s">
         <v>159</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>161</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>15</v>
@@ -2858,25 +2846,25 @@
     </row>
     <row r="31" ht="60" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E31" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="B31" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="C31" s="3" t="s">
+      <c r="F31" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="D31" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E31" s="3" t="s">
+      <c r="G31" s="3" t="s">
         <v>164</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="G31" s="3" t="s">
-        <v>166</v>
       </c>
       <c r="H31" s="3" t="s">
         <v>15</v>
@@ -2884,25 +2872,25 @@
     </row>
     <row r="32" ht="60" customHeight="1" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E32" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="B32" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="C32" s="2" t="s">
+      <c r="F32" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="D32" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E32" s="2" t="s">
+      <c r="G32" s="2" t="s">
         <v>169</v>
-      </c>
-      <c r="F32" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="G32" s="2" t="s">
-        <v>171</v>
       </c>
       <c r="H32" s="2" t="s">
         <v>15</v>
@@ -2910,25 +2898,25 @@
     </row>
     <row r="33" ht="60" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E33" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="B33" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="C33" s="3" t="s">
+      <c r="F33" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="D33" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E33" s="3" t="s">
+      <c r="G33" s="3" t="s">
         <v>174</v>
-      </c>
-      <c r="F33" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="G33" s="3" t="s">
-        <v>176</v>
       </c>
       <c r="H33" s="3" t="s">
         <v>15</v>
@@ -2936,25 +2924,25 @@
     </row>
     <row r="34" ht="60" customHeight="1" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E34" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="B34" s="2" t="s">
+      <c r="F34" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="C34" s="2" t="s">
+      <c r="G34" s="2" t="s">
         <v>179</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="F34" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="G34" s="2" t="s">
-        <v>182</v>
       </c>
       <c r="H34" s="2" t="s">
         <v>15</v>
@@ -2962,25 +2950,25 @@
     </row>
     <row r="35" ht="60" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="F35" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="B35" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="C35" s="3" t="s">
+      <c r="G35" s="3" t="s">
         <v>184</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E35" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="F35" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="G35" s="3" t="s">
-        <v>187</v>
       </c>
       <c r="H35" s="3" t="s">
         <v>15</v>
@@ -2988,25 +2976,25 @@
     </row>
     <row r="36" ht="60" customHeight="1" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="F36" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="B36" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="C36" s="2" t="s">
+      <c r="G36" s="2" t="s">
         <v>189</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="F36" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="G36" s="2" t="s">
-        <v>192</v>
       </c>
       <c r="H36" s="2" t="s">
         <v>15</v>
@@ -3014,25 +3002,25 @@
     </row>
     <row r="37" ht="60" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="F37" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="B37" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="C37" s="3" t="s">
+      <c r="G37" s="3" t="s">
         <v>194</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E37" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="F37" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="G37" s="3" t="s">
-        <v>197</v>
       </c>
       <c r="H37" s="3" t="s">
         <v>15</v>
@@ -3040,25 +3028,25 @@
     </row>
     <row r="38" ht="60" customHeight="1" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="F38" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="B38" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="C38" s="2" t="s">
+      <c r="G38" s="2" t="s">
         <v>199</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="F38" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="G38" s="2" t="s">
-        <v>202</v>
       </c>
       <c r="H38" s="2" t="s">
         <v>15</v>
@@ -3066,25 +3054,25 @@
     </row>
     <row r="39" ht="60" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E39" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="B39" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="C39" s="3" t="s">
+      <c r="F39" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="D39" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E39" s="3" t="s">
+      <c r="G39" s="3" t="s">
         <v>205</v>
-      </c>
-      <c r="F39" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="G39" s="3" t="s">
-        <v>207</v>
       </c>
       <c r="H39" s="3" t="s">
         <v>15</v>
@@ -3092,25 +3080,25 @@
     </row>
     <row r="40" ht="60" customHeight="1" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E40" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="B40" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="C40" s="2" t="s">
+      <c r="F40" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="D40" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E40" s="2" t="s">
+      <c r="G40" s="2" t="s">
         <v>210</v>
-      </c>
-      <c r="F40" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="G40" s="2" t="s">
-        <v>212</v>
       </c>
       <c r="H40" s="2" t="s">
         <v>15</v>
@@ -3118,25 +3106,25 @@
     </row>
     <row r="41" ht="60" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E41" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="B41" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="C41" s="3" t="s">
+      <c r="F41" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="D41" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E41" s="3" t="s">
+      <c r="G41" s="3" t="s">
         <v>215</v>
-      </c>
-      <c r="F41" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="G41" s="3" t="s">
-        <v>217</v>
       </c>
       <c r="H41" s="3" t="s">
         <v>15</v>
@@ -3144,25 +3132,25 @@
     </row>
     <row r="42" ht="60" customHeight="1" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E42" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="B42" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="C42" s="2" t="s">
+      <c r="F42" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="D42" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E42" s="2" t="s">
+      <c r="G42" s="2" t="s">
         <v>220</v>
-      </c>
-      <c r="F42" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="G42" s="2" t="s">
-        <v>222</v>
       </c>
       <c r="H42" s="2" t="s">
         <v>15</v>
@@ -3170,25 +3158,25 @@
     </row>
     <row r="43" ht="60" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E43" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="B43" s="3" t="s">
+      <c r="F43" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="C43" s="3" t="s">
+      <c r="G43" s="3" t="s">
         <v>225</v>
-      </c>
-      <c r="D43" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E43" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="F43" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="G43" s="3" t="s">
-        <v>228</v>
       </c>
       <c r="H43" s="3" t="s">
         <v>15</v>
@@ -3196,25 +3184,25 @@
     </row>
     <row r="44" ht="60" customHeight="1" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="F44" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="B44" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="C44" s="2" t="s">
+      <c r="G44" s="2" t="s">
         <v>230</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="F44" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="G44" s="2" t="s">
-        <v>233</v>
       </c>
       <c r="H44" s="2" t="s">
         <v>15</v>
@@ -3222,25 +3210,25 @@
     </row>
     <row r="45" ht="60" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="F45" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="B45" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="C45" s="3" t="s">
+      <c r="G45" s="3" t="s">
         <v>235</v>
-      </c>
-      <c r="D45" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E45" s="3" t="s">
-        <v>236</v>
-      </c>
-      <c r="F45" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="G45" s="3" t="s">
-        <v>238</v>
       </c>
       <c r="H45" s="3" t="s">
         <v>15</v>
@@ -3248,25 +3236,25 @@
     </row>
     <row r="46" ht="60" customHeight="1" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E46" s="2" t="s">
         <v>239</v>
       </c>
-      <c r="B46" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="C46" s="2" t="s">
+      <c r="F46" s="2" t="s">
         <v>240</v>
       </c>
-      <c r="D46" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E46" s="2" t="s">
+      <c r="G46" s="2" t="s">
         <v>241</v>
-      </c>
-      <c r="F46" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="G46" s="2" t="s">
-        <v>243</v>
       </c>
       <c r="H46" s="2" t="s">
         <v>15</v>
@@ -3274,25 +3262,25 @@
     </row>
     <row r="47" ht="60" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E47" s="3" t="s">
         <v>244</v>
       </c>
-      <c r="B47" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="C47" s="3" t="s">
+      <c r="F47" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="D47" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E47" s="3" t="s">
+      <c r="G47" s="3" t="s">
         <v>246</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="G47" s="3" t="s">
-        <v>248</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>15</v>
@@ -3300,25 +3288,25 @@
     </row>
     <row r="48" ht="60" customHeight="1" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E48" s="2" t="s">
         <v>249</v>
       </c>
-      <c r="B48" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="C48" s="2" t="s">
+      <c r="F48" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="D48" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E48" s="2" t="s">
+      <c r="G48" s="2" t="s">
         <v>251</v>
-      </c>
-      <c r="F48" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="G48" s="2" t="s">
-        <v>253</v>
       </c>
       <c r="H48" s="2" t="s">
         <v>15</v>
@@ -3326,25 +3314,25 @@
     </row>
     <row r="49" ht="60" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E49" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="B49" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="C49" s="3" t="s">
+      <c r="F49" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="D49" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E49" s="3" t="s">
+      <c r="G49" s="3" t="s">
         <v>256</v>
-      </c>
-      <c r="F49" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="G49" s="3" t="s">
-        <v>258</v>
       </c>
       <c r="H49" s="3" t="s">
         <v>15</v>
@@ -3352,25 +3340,25 @@
     </row>
     <row r="50" ht="60" customHeight="1" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E50" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="B50" s="2" t="s">
+      <c r="F50" s="2" t="s">
         <v>260</v>
       </c>
-      <c r="C50" s="2" t="s">
+      <c r="G50" s="2" t="s">
         <v>261</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E50" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="F50" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="G50" s="2" t="s">
-        <v>264</v>
       </c>
       <c r="H50" s="2" t="s">
         <v>15</v>
@@ -3378,25 +3366,25 @@
     </row>
     <row r="51" ht="60" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E51" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="F51" s="3" t="s">
         <v>265</v>
       </c>
-      <c r="B51" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="C51" s="3" t="s">
+      <c r="G51" s="3" t="s">
         <v>266</v>
-      </c>
-      <c r="D51" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E51" s="3" t="s">
-        <v>267</v>
-      </c>
-      <c r="F51" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="G51" s="3" t="s">
-        <v>269</v>
       </c>
       <c r="H51" s="3" t="s">
         <v>15</v>
@@ -3404,25 +3392,25 @@
     </row>
     <row r="52" ht="60" customHeight="1" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="F52" s="2" t="s">
         <v>270</v>
       </c>
-      <c r="B52" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="C52" s="2" t="s">
+      <c r="G52" s="2" t="s">
         <v>271</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E52" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="F52" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="G52" s="2" t="s">
-        <v>274</v>
       </c>
       <c r="H52" s="2" t="s">
         <v>15</v>
@@ -3430,25 +3418,25 @@
     </row>
     <row r="53" ht="60" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E53" s="3" t="s">
         <v>275</v>
       </c>
-      <c r="B53" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="C53" s="3" t="s">
+      <c r="F53" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="D53" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E53" s="3" t="s">
+      <c r="G53" s="3" t="s">
         <v>277</v>
-      </c>
-      <c r="F53" s="3" t="s">
-        <v>278</v>
-      </c>
-      <c r="G53" s="3" t="s">
-        <v>279</v>
       </c>
       <c r="H53" s="3" t="s">
         <v>15</v>
@@ -3456,25 +3444,25 @@
     </row>
     <row r="54" ht="60" customHeight="1" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E54" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="B54" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="C54" s="2" t="s">
+      <c r="F54" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="D54" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E54" s="2" t="s">
+      <c r="G54" s="2" t="s">
         <v>282</v>
-      </c>
-      <c r="F54" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="G54" s="2" t="s">
-        <v>284</v>
       </c>
       <c r="H54" s="2" t="s">
         <v>15</v>
@@ -3482,25 +3470,25 @@
     </row>
     <row r="55" ht="60" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E55" s="3" t="s">
         <v>285</v>
       </c>
-      <c r="B55" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="C55" s="3" t="s">
+      <c r="F55" s="3" t="s">
         <v>286</v>
       </c>
-      <c r="D55" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E55" s="3" t="s">
+      <c r="G55" s="3" t="s">
         <v>287</v>
-      </c>
-      <c r="F55" s="3" t="s">
-        <v>288</v>
-      </c>
-      <c r="G55" s="3" t="s">
-        <v>289</v>
       </c>
       <c r="H55" s="3" t="s">
         <v>15</v>
@@ -3508,16 +3496,16 @@
     </row>
     <row r="56" ht="60" customHeight="1" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="C56" s="2" t="s">
         <v>290</v>
       </c>
-      <c r="B56" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="C56" s="2" t="s">
+      <c r="D56" s="2" t="s">
         <v>291</v>
-      </c>
-      <c r="D56" s="2" t="s">
-        <v>11</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>292</v>
@@ -3537,13 +3525,13 @@
         <v>295</v>
       </c>
       <c r="B57" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="C57" s="3" t="s">
         <v>296</v>
       </c>
-      <c r="C57" s="3" t="s">
+      <c r="D57" s="3" t="s">
         <v>297</v>
-      </c>
-      <c r="D57" s="3" t="s">
-        <v>11</v>
       </c>
       <c r="E57" s="3" t="s">
         <v>298</v>
@@ -3563,22 +3551,22 @@
         <v>301</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>296</v>
+        <v>289</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>302</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>11</v>
+        <v>303</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H58" s="2" t="s">
         <v>15</v>
@@ -3586,25 +3574,25 @@
     </row>
     <row r="59" ht="60" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>296</v>
+        <v>308</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>11</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="G59" s="3" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="H59" s="3" t="s">
         <v>15</v>
@@ -3612,16 +3600,16 @@
     </row>
     <row r="60" ht="60" customHeight="1" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>314</v>
+        <v>11</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>315</v>
@@ -3641,7 +3629,7 @@
         <v>318</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="C61" s="3" t="s">
         <v>319</v>
@@ -3667,7 +3655,7 @@
         <v>324</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>325</v>
@@ -3751,16 +3739,16 @@
         <v>343</v>
       </c>
       <c r="D65" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="E65" s="3" t="s">
         <v>344</v>
       </c>
-      <c r="E65" s="3" t="s">
+      <c r="F65" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="G65" s="3" t="s">
         <v>345</v>
-      </c>
-      <c r="F65" s="3" t="s">
-        <v>346</v>
-      </c>
-      <c r="G65" s="3" t="s">
-        <v>347</v>
       </c>
       <c r="H65" s="3" t="s">
         <v>15</v>
@@ -3768,25 +3756,25 @@
     </row>
     <row r="66" ht="60" customHeight="1" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>331</v>
       </c>
       <c r="C66" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="F66" s="2" t="s">
         <v>349</v>
       </c>
-      <c r="D66" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="E66" s="2" t="s">
+      <c r="G66" s="2" t="s">
         <v>350</v>
-      </c>
-      <c r="F66" s="2" t="s">
-        <v>351</v>
-      </c>
-      <c r="G66" s="2" t="s">
-        <v>352</v>
       </c>
       <c r="H66" s="2" t="s">
         <v>15</v>
@@ -3794,25 +3782,25 @@
     </row>
     <row r="67" ht="60" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="B67" s="3" t="s">
         <v>331</v>
       </c>
       <c r="C67" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="E67" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="F67" s="3" t="s">
         <v>354</v>
       </c>
-      <c r="D67" s="3" t="s">
-        <v>344</v>
-      </c>
-      <c r="E67" s="3" t="s">
+      <c r="G67" s="3" t="s">
         <v>355</v>
-      </c>
-      <c r="F67" s="3" t="s">
-        <v>356</v>
-      </c>
-      <c r="G67" s="3" t="s">
-        <v>357</v>
       </c>
       <c r="H67" s="3" t="s">
         <v>15</v>
@@ -3820,25 +3808,25 @@
     </row>
     <row r="68" ht="60" customHeight="1" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>331</v>
       </c>
       <c r="C68" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="F68" s="2" t="s">
         <v>359</v>
       </c>
-      <c r="D68" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="E68" s="2" t="s">
+      <c r="G68" s="2" t="s">
         <v>360</v>
-      </c>
-      <c r="F68" s="2" t="s">
-        <v>361</v>
-      </c>
-      <c r="G68" s="2" t="s">
-        <v>362</v>
       </c>
       <c r="H68" s="2" t="s">
         <v>15</v>
@@ -3846,25 +3834,25 @@
     </row>
     <row r="69" ht="60" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="B69" s="3" t="s">
         <v>331</v>
       </c>
       <c r="C69" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="D69" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="E69" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="F69" s="3" t="s">
         <v>364</v>
       </c>
-      <c r="D69" s="3" t="s">
-        <v>344</v>
-      </c>
-      <c r="E69" s="3" t="s">
+      <c r="G69" s="3" t="s">
         <v>365</v>
-      </c>
-      <c r="F69" s="3" t="s">
-        <v>366</v>
-      </c>
-      <c r="G69" s="3" t="s">
-        <v>367</v>
       </c>
       <c r="H69" s="3" t="s">
         <v>15</v>
@@ -3872,25 +3860,25 @@
     </row>
     <row r="70" ht="60" customHeight="1" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>331</v>
       </c>
       <c r="C70" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="F70" s="2" t="s">
         <v>369</v>
       </c>
-      <c r="D70" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="E70" s="2" t="s">
+      <c r="G70" s="2" t="s">
         <v>370</v>
-      </c>
-      <c r="F70" s="2" t="s">
-        <v>371</v>
-      </c>
-      <c r="G70" s="2" t="s">
-        <v>372</v>
       </c>
       <c r="H70" s="2" t="s">
         <v>15</v>
@@ -3898,25 +3886,25 @@
     </row>
     <row r="71" ht="60" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="B71" s="3" t="s">
         <v>331</v>
       </c>
       <c r="C71" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="D71" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="E71" s="3" t="s">
         <v>374</v>
       </c>
-      <c r="D71" s="3" t="s">
+      <c r="F71" s="3" t="s">
         <v>375</v>
       </c>
-      <c r="E71" s="3" t="s">
+      <c r="G71" s="3" t="s">
         <v>376</v>
-      </c>
-      <c r="F71" s="3" t="s">
-        <v>377</v>
-      </c>
-      <c r="G71" s="3" t="s">
-        <v>378</v>
       </c>
       <c r="H71" s="3" t="s">
         <v>15</v>
@@ -3924,25 +3912,25 @@
     </row>
     <row r="72" ht="60" customHeight="1" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>331</v>
       </c>
       <c r="C72" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="F72" s="2" t="s">
         <v>380</v>
       </c>
-      <c r="D72" s="2" t="s">
+      <c r="G72" s="2" t="s">
         <v>381</v>
-      </c>
-      <c r="E72" s="2" t="s">
-        <v>382</v>
-      </c>
-      <c r="F72" s="2" t="s">
-        <v>383</v>
-      </c>
-      <c r="G72" s="2" t="s">
-        <v>384</v>
       </c>
       <c r="H72" s="2" t="s">
         <v>15</v>
@@ -3950,25 +3938,25 @@
     </row>
     <row r="73" ht="60" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A73" s="3" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="B73" s="3" t="s">
         <v>331</v>
       </c>
       <c r="C73" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="D73" s="3" t="s">
+        <v>384</v>
+      </c>
+      <c r="E73" s="3" t="s">
+        <v>385</v>
+      </c>
+      <c r="F73" s="3" t="s">
         <v>386</v>
       </c>
-      <c r="D73" s="3" t="s">
+      <c r="G73" s="3" t="s">
         <v>387</v>
-      </c>
-      <c r="E73" s="3" t="s">
-        <v>388</v>
-      </c>
-      <c r="F73" s="3" t="s">
-        <v>389</v>
-      </c>
-      <c r="G73" s="3" t="s">
-        <v>390</v>
       </c>
       <c r="H73" s="3" t="s">
         <v>15</v>
@@ -3976,25 +3964,25 @@
     </row>
     <row r="74" ht="60" customHeight="1" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="B74" s="2" t="s">
         <v>331</v>
       </c>
       <c r="C74" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="F74" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="G74" s="2" t="s">
         <v>392</v>
-      </c>
-      <c r="D74" s="2" t="s">
-        <v>381</v>
-      </c>
-      <c r="E74" s="2" t="s">
-        <v>393</v>
-      </c>
-      <c r="F74" s="2" t="s">
-        <v>394</v>
-      </c>
-      <c r="G74" s="2" t="s">
-        <v>395</v>
       </c>
       <c r="H74" s="2" t="s">
         <v>15</v>
@@ -4002,25 +3990,25 @@
     </row>
     <row r="75" ht="60" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A75" s="3" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="B75" s="3" t="s">
         <v>331</v>
       </c>
       <c r="C75" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="D75" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="E75" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="F75" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="G75" s="3" t="s">
         <v>397</v>
-      </c>
-      <c r="D75" s="3" t="s">
-        <v>381</v>
-      </c>
-      <c r="E75" s="3" t="s">
-        <v>398</v>
-      </c>
-      <c r="F75" s="3" t="s">
-        <v>399</v>
-      </c>
-      <c r="G75" s="3" t="s">
-        <v>400</v>
       </c>
       <c r="H75" s="3" t="s">
         <v>15</v>
@@ -4028,25 +4016,25 @@
     </row>
     <row r="76" ht="60" customHeight="1" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="B76" s="2" t="s">
         <v>331</v>
       </c>
       <c r="C76" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="F76" s="2" t="s">
         <v>402</v>
       </c>
-      <c r="D76" s="2" t="s">
+      <c r="G76" s="2" t="s">
         <v>403</v>
-      </c>
-      <c r="E76" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="F76" s="2" t="s">
-        <v>405</v>
-      </c>
-      <c r="G76" s="2" t="s">
-        <v>406</v>
       </c>
       <c r="H76" s="2" t="s">
         <v>15</v>
@@ -4054,25 +4042,25 @@
     </row>
     <row r="77" ht="60" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A77" s="3" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="B77" s="3" t="s">
         <v>331</v>
       </c>
       <c r="C77" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="D77" s="3" t="s">
+        <v>400</v>
+      </c>
+      <c r="E77" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="F77" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="G77" s="3" t="s">
         <v>408</v>
-      </c>
-      <c r="D77" s="3" t="s">
-        <v>403</v>
-      </c>
-      <c r="E77" s="3" t="s">
-        <v>409</v>
-      </c>
-      <c r="F77" s="3" t="s">
-        <v>410</v>
-      </c>
-      <c r="G77" s="3" t="s">
-        <v>411</v>
       </c>
       <c r="H77" s="3" t="s">
         <v>15</v>
@@ -4080,25 +4068,25 @@
     </row>
     <row r="78" ht="60" customHeight="1" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="B78" s="2" t="s">
         <v>331</v>
       </c>
       <c r="C78" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="E78" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="F78" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="G78" s="2" t="s">
         <v>413</v>
-      </c>
-      <c r="D78" s="2" t="s">
-        <v>403</v>
-      </c>
-      <c r="E78" s="2" t="s">
-        <v>414</v>
-      </c>
-      <c r="F78" s="2" t="s">
-        <v>415</v>
-      </c>
-      <c r="G78" s="2" t="s">
-        <v>416</v>
       </c>
       <c r="H78" s="2" t="s">
         <v>15</v>
@@ -4106,25 +4094,25 @@
     </row>
     <row r="79" ht="60" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A79" s="3" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="B79" s="3" t="s">
         <v>331</v>
       </c>
       <c r="C79" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="D79" s="3" t="s">
+        <v>400</v>
+      </c>
+      <c r="E79" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="F79" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="G79" s="3" t="s">
         <v>418</v>
-      </c>
-      <c r="D79" s="3" t="s">
-        <v>403</v>
-      </c>
-      <c r="E79" s="3" t="s">
-        <v>419</v>
-      </c>
-      <c r="F79" s="3" t="s">
-        <v>420</v>
-      </c>
-      <c r="G79" s="3" t="s">
-        <v>421</v>
       </c>
       <c r="H79" s="3" t="s">
         <v>15</v>
@@ -4132,25 +4120,25 @@
     </row>
     <row r="80" ht="60" customHeight="1" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="B80" s="2" t="s">
         <v>331</v>
       </c>
       <c r="C80" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="E80" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="F80" s="2" t="s">
         <v>423</v>
       </c>
-      <c r="D80" s="2" t="s">
+      <c r="G80" s="2" t="s">
         <v>424</v>
-      </c>
-      <c r="E80" s="2" t="s">
-        <v>425</v>
-      </c>
-      <c r="F80" s="2" t="s">
-        <v>426</v>
-      </c>
-      <c r="G80" s="2" t="s">
-        <v>427</v>
       </c>
       <c r="H80" s="2" t="s">
         <v>15</v>
@@ -4158,25 +4146,25 @@
     </row>
     <row r="81" ht="60" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A81" s="3" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="B81" s="3" t="s">
         <v>331</v>
       </c>
       <c r="C81" s="3" t="s">
+        <v>426</v>
+      </c>
+      <c r="D81" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="F81" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="G81" s="3" t="s">
         <v>429</v>
-      </c>
-      <c r="D81" s="3" t="s">
-        <v>430</v>
-      </c>
-      <c r="E81" s="3" t="s">
-        <v>431</v>
-      </c>
-      <c r="F81" s="3" t="s">
-        <v>432</v>
-      </c>
-      <c r="G81" s="3" t="s">
-        <v>433</v>
       </c>
       <c r="H81" s="3" t="s">
         <v>15</v>
@@ -4184,25 +4172,25 @@
     </row>
     <row r="82" ht="60" customHeight="1" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="B82" s="2" t="s">
         <v>331</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>430</v>
+        <v>421</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="H82" s="2" t="s">
         <v>15</v>
@@ -4210,25 +4198,25 @@
     </row>
     <row r="83" ht="60" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A83" s="3" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="B83" s="3" t="s">
         <v>331</v>
       </c>
       <c r="C83" s="3" t="s">
+        <v>436</v>
+      </c>
+      <c r="D83" s="3" t="s">
+        <v>437</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>438</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>439</v>
+      </c>
+      <c r="G83" s="3" t="s">
         <v>440</v>
-      </c>
-      <c r="D83" s="3" t="s">
-        <v>441</v>
-      </c>
-      <c r="E83" s="3" t="s">
-        <v>442</v>
-      </c>
-      <c r="F83" s="3" t="s">
-        <v>443</v>
-      </c>
-      <c r="G83" s="3" t="s">
-        <v>444</v>
       </c>
       <c r="H83" s="3" t="s">
         <v>15</v>
@@ -4236,25 +4224,25 @@
     </row>
     <row r="84" ht="60" customHeight="1" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="B84" s="2" t="s">
         <v>331</v>
       </c>
       <c r="C84" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="E84" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="F84" s="2" t="s">
+        <v>445</v>
+      </c>
+      <c r="G84" s="2" t="s">
         <v>446</v>
-      </c>
-      <c r="D84" s="2" t="s">
-        <v>447</v>
-      </c>
-      <c r="E84" s="2" t="s">
-        <v>448</v>
-      </c>
-      <c r="F84" s="2" t="s">
-        <v>449</v>
-      </c>
-      <c r="G84" s="2" t="s">
-        <v>450</v>
       </c>
       <c r="H84" s="2" t="s">
         <v>15</v>
@@ -4262,12 +4250,12 @@
     </row>
     <row r="87" spans="1:1" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A87" s="4" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
     </row>
     <row r="89" spans="1:2" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A89" s="5" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="B89" s="5">
         <v>83</v>
@@ -4275,7 +4263,7 @@
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="B90">
         <v>7</v>
@@ -4283,7 +4271,7 @@
     </row>
     <row r="91" spans="1:2" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A91" s="5" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="B91" s="5">
         <v>7</v>
@@ -4291,7 +4279,7 @@
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="B92">
         <v>7</v>
@@ -4299,31 +4287,31 @@
     </row>
     <row r="93" spans="1:2" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A93" s="5" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="B93" s="5">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="B94">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="95" spans="1:2" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A95" s="5" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="B95" s="5">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="B96">
         <v>7</v>
@@ -4331,15 +4319,15 @@
     </row>
     <row r="97" spans="1:2" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A97" s="5" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="B97" s="5">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="B98">
         <v>3</v>
@@ -4347,7 +4335,7 @@
     </row>
     <row r="99" spans="1:2" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A99" s="5" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="B99" s="5">
         <v>3</v>
@@ -4355,7 +4343,7 @@
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="B100">
         <v>22</v>
